--- a/InputData/indst/_cement/BCD/BAU Cement Demand.xlsx
+++ b/InputData/indst/_cement/BCD/BAU Cement Demand.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\BCD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34ED2B25-05E8-4ECD-842D-E602D10FD575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A24251E-2E6F-4468-BB45-E85A8447AEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -481,36 +481,36 @@
     <t>Rough estimate: USGS production of 44 million tons (2025 estimate, from the USGS source) minus about 3.9 million tons of 2024 clinker exports gives roughly 40 million tons. The Japan Cement Association publishes better data and should replace this estimate.</t>
   </si>
   <si>
+    <t>We set this file up to be adaptable to each of the main EPS regions. If you are working on a non-US region, use the drop-down selector at the top of the 'Regions' tab to choose a different country. The Derivation then grows that country's starting consumption at the annual growth rate listed for it, or holds it flat if no rate is listed, and the 'BCD' tab updates on its own; just re-export the CSV. If your region is not listed, you will have to build the demand forecast on your own.</t>
+  </si>
+  <si>
+    <t>Pick a region from the drop-down in B1. The Derivation and the export tab update on their own; re-export the CSV afterward. A blank cell means no sourced value yet.</t>
+  </si>
+  <si>
+    <t>CemNet citing demand data (SNIPPET). 2025 projection 1,790 (ICR via Cement Europe, SNIPPET); NBS 2025 production 1,670-1,693 (SNIPPET); 2024 fell ~8-10% y/y. Long-run CAGR TO FILL (IEA 2018 roadmap: China declines to 2050, no number).</t>
+  </si>
+  <si>
+    <t>FY2024-25 (Apr 2024-Mar 2025, assigned to 2024) consumption 435 / production 427, ACEEE Jul-2026 citing IBEF. USGS gives calendar-year production of 440 (2024e) and 470 (2025e). | CAGR (2023-70): NITI Aayog Jan-2026 path 391 (2023) -&gt; 2,100 Mt (2070) (SNIPPET); CAGR is own arithmetic. Front-loaded path: 7.8%/yr 2023-30, 5.9%/yr 2030-47; GCCA India/TERI ~3.1%/yr; IEA 2018 'triple by 2050' ~3.1%/yr. A flat CAGR understates near-term growth.</t>
+  </si>
+  <si>
+    <t>Cement Europe Statistics Report 2025, EU-27 scope (DIRECT). Production 160.8 (2024, DIRECT). UNRESOLVED: production - consumption = +12.7 Mt vs ~0 Eurostat net trade - ask Cement Europe. Do not mix with the 165.1 wider-membership figure.</t>
+  </si>
+  <si>
+    <t>SNIC Annual Report 2023 apparent consumption (DIRECT). Other figures: 2024 SNIC sales 64.652 (via CemNet, SNIPPET); 2024 consumption 64.8 and 2025 dispatches 66.984 (SNIPPET). A 73 Mt 2024 'consumption' figure in secondary sources is unreliable. | CAGR (2014-50): SNIC/IEA/WBCSD 2019 roadmap: demand +60% (low) to +120% (high) vs 2014 by 2050 (DIRECT) = 1.3-2.2%/yr; 1.7%/yr chosen within the range (judgment). Applied from the 2023 anchor, which sits below the 2014 base, so 2050 lands under the roadmap low case.</t>
+  </si>
+  <si>
+    <t>~42 Mt 2024 sales (Cementos Moctezuma CEO via Global Cement, SNIPPET). CONFLICT: a 2024 CANACEM forecast via Global Cement gives 46.4 - resolve against CANACEM statistics. 2025 consumption -6% (SNIPPET).</t>
+  </si>
+  <si>
+    <t>Asperssi (ASI) 2025 domestic sales, used as apparent consumption (imports negligible) (DIRECT). 2024: 64.895. Production 64.720 (2025).</t>
+  </si>
+  <si>
+    <t>Unit: metric tons/year</t>
+  </si>
+  <si>
     <t>This file gives the business-as-usual demand for cement in the region, in metric tons per year, for 2021-2050. It drives the EPS cement module: how much clinker the region needs, and from that the kiln capacity, energy use, and process emissions of the cement industry.
 The demand is total cement consumption, including cement and clinker the region imports. The model takes out the share supplied by net imports later (using the BFoCDMbNI file), so only cement made in the region uses energy and produces emissions.
-The tabs run from inputs to output. 'Regions' holds the region selector and each region's starting consumption and growth rate. 'USGS MCS 2026 Cement' and 'AEO 2026 Table 23' hold the U.S. source data as published. 'Derivation' builds the 2021-2050 series, and the 'BCD' tab reads from it, rounded to whole tons. The 'BCD' tab is what gets exported to BCD.csv.</t>
-  </si>
-  <si>
-    <t>We set this file up to be adaptable to each of the main EPS regions. If you are working on a non-US region, use the drop-down selector at the top of the 'Regions' tab to choose a different country. The Derivation then grows that country's starting consumption at the annual growth rate listed for it, or holds it flat if no rate is listed, and the 'BCD' tab updates on its own; just re-export the CSV. If your region is not listed, you will have to build the demand forecast on your own.</t>
-  </si>
-  <si>
-    <t>Pick a region from the drop-down in B1. The Derivation and the export tab update on their own; re-export the CSV afterward. A blank cell means no sourced value yet.</t>
-  </si>
-  <si>
-    <t>CemNet citing demand data (SNIPPET). 2025 projection 1,790 (ICR via Cement Europe, SNIPPET); NBS 2025 production 1,670-1,693 (SNIPPET); 2024 fell ~8-10% y/y. Long-run CAGR TO FILL (IEA 2018 roadmap: China declines to 2050, no number).</t>
-  </si>
-  <si>
-    <t>FY2024-25 (Apr 2024-Mar 2025, assigned to 2024) consumption 435 / production 427, ACEEE Jul-2026 citing IBEF. USGS gives calendar-year production of 440 (2024e) and 470 (2025e). | CAGR (2023-70): NITI Aayog Jan-2026 path 391 (2023) -&gt; 2,100 Mt (2070) (SNIPPET); CAGR is own arithmetic. Front-loaded path: 7.8%/yr 2023-30, 5.9%/yr 2030-47; GCCA India/TERI ~3.1%/yr; IEA 2018 'triple by 2050' ~3.1%/yr. A flat CAGR understates near-term growth.</t>
-  </si>
-  <si>
-    <t>Cement Europe Statistics Report 2025, EU-27 scope (DIRECT). Production 160.8 (2024, DIRECT). UNRESOLVED: production - consumption = +12.7 Mt vs ~0 Eurostat net trade - ask Cement Europe. Do not mix with the 165.1 wider-membership figure.</t>
-  </si>
-  <si>
-    <t>SNIC Annual Report 2023 apparent consumption (DIRECT). Other figures: 2024 SNIC sales 64.652 (via CemNet, SNIPPET); 2024 consumption 64.8 and 2025 dispatches 66.984 (SNIPPET). A 73 Mt 2024 'consumption' figure in secondary sources is unreliable. | CAGR (2014-50): SNIC/IEA/WBCSD 2019 roadmap: demand +60% (low) to +120% (high) vs 2014 by 2050 (DIRECT) = 1.3-2.2%/yr; 1.7%/yr chosen within the range (judgment). Applied from the 2023 anchor, which sits below the 2014 base, so 2050 lands under the roadmap low case.</t>
-  </si>
-  <si>
-    <t>~42 Mt 2024 sales (Cementos Moctezuma CEO via Global Cement, SNIPPET). CONFLICT: a 2024 CANACEM forecast via Global Cement gives 46.4 - resolve against CANACEM statistics. 2025 consumption -6% (SNIPPET).</t>
-  </si>
-  <si>
-    <t>Asperssi (ASI) 2025 domestic sales, used as apparent consumption (imports negligible) (DIRECT). 2024: 64.895. Production 64.720 (2025).</t>
-  </si>
-  <si>
-    <t>Unit: metric tons/year</t>
+The tabs run from inputs to output. 'Regions' holds the region selector and each region's starting consumption and growth rate. 'USGS MCS 2026 Cement' and 'AEO 2026 Table 23' hold the U.S. source data as published. 'Derivation' builds the 2021-2050 series, and the 'BCD' tab reads from it. The 'BCD' tab is what gets exported to BCD.csv.</t>
   </si>
 </sst>
 </file>
@@ -529,12 +529,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -594,7 +596,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -617,6 +619,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -923,20 +928,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D57"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="110.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
-    <col min="4" max="4" width="110.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" customWidth="1"/>
+    <col min="2" max="2" width="110.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.6328125" customWidth="1"/>
+    <col min="4" max="4" width="110.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
@@ -947,31 +952,31 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B6" s="10">
         <v>2026</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="10">
         <v>2024</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B7" s="9" t="s">
         <v>5</v>
       </c>
@@ -979,15 +984,15 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B10" s="8" t="s">
         <v>7</v>
       </c>
@@ -995,31 +1000,31 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B11" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="10" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B12" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="10" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B13" s="10">
         <v>2026</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="10">
         <v>2019</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B14" s="9" t="s">
         <v>10</v>
       </c>
@@ -1027,15 +1032,15 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B15" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="8" t="s">
         <v>12</v>
       </c>
@@ -1043,31 +1048,31 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B18" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="10" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B19" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="2">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B20" s="10">
         <v>2025</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="10">
         <v>2025</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="9" t="s">
         <v>15</v>
       </c>
@@ -1075,15 +1080,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B22" s="2" t="s">
+    <row r="22" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B22" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="8" t="s">
         <v>17</v>
       </c>
@@ -1091,31 +1096,31 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B25" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="s">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B26" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="10" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="2">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B27" s="10">
         <v>2026</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="10">
         <v>2023</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="9" t="s">
         <v>20</v>
       </c>
@@ -1123,15 +1128,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="2:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="B29" s="2" t="s">
+    <row r="29" spans="2:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="B29" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="8" t="s">
         <v>22</v>
       </c>
@@ -1139,31 +1144,31 @@
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B32" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="10" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B33" s="2" t="s">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B33" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="2">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B34" s="10">
         <v>2026</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="10">
         <v>2026</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="9" t="s">
         <v>25</v>
       </c>
@@ -1171,15 +1176,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
+    <row r="36" spans="2:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B36" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="10" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="8" t="s">
         <v>27</v>
       </c>
@@ -1187,31 +1192,31 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B39" s="2" t="s">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B39" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="10" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B40" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="10" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B41" s="2">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B41" s="10">
         <v>2025</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="10">
         <v>2026</v>
       </c>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B42" s="9" t="s">
         <v>30</v>
       </c>
@@ -1219,96 +1224,96 @@
         <v>64</v>
       </c>
     </row>
-    <row r="43" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
+    <row r="43" spans="2:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B43" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B45" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B46" s="2" t="s">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B46" s="10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="s">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B47" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B48" s="2">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B48" s="10">
         <v>2024</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B49" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="B50" s="2" t="s">
+    <row r="50" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B50" s="10" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="180" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" ht="145" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="B54" s="10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="B55" s="10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="10" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="105" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="10" t="s">
         <v>72</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{8A2B5619-3B38-453F-9575-77612E65D573}"/>
-    <hyperlink ref="B14" r:id="rId2" xr:uid="{F944C45C-BB4B-40B1-A30E-73F0002D43A7}"/>
-    <hyperlink ref="B21" r:id="rId3" xr:uid="{B57EA0B3-2670-43AD-BE16-5F3DB0892192}"/>
-    <hyperlink ref="B28" r:id="rId4" xr:uid="{5CF85B0C-2573-4898-8BEB-FC3B92BEE160}"/>
-    <hyperlink ref="B35" r:id="rId5" xr:uid="{A407E95D-871B-43CE-83DC-6322DF49B4FA}"/>
-    <hyperlink ref="B42" r:id="rId6" xr:uid="{DFE4ED27-C85F-4A61-95F9-01BA22D41D53}"/>
-    <hyperlink ref="B49" r:id="rId7" xr:uid="{2B6C990D-F3F9-4A76-8737-EBFCFC64D894}"/>
-    <hyperlink ref="D7" r:id="rId8" xr:uid="{9DCE14A3-CD13-420B-A15A-A9A9351CD29B}"/>
-    <hyperlink ref="D14" r:id="rId9" xr:uid="{CE9A1A12-3182-4D4F-9518-5840CF1C846B}"/>
-    <hyperlink ref="D21" r:id="rId10" xr:uid="{663FB71B-0803-4301-8C18-709E134D441B}"/>
-    <hyperlink ref="D28" r:id="rId11" xr:uid="{A945EFAA-F817-4F8D-8D0C-D2F0209D820C}"/>
-    <hyperlink ref="D35" r:id="rId12" xr:uid="{A0A3014D-0FAF-44A2-BD74-9FEB0474CD27}"/>
-    <hyperlink ref="D42" r:id="rId13" xr:uid="{05B601A8-E5F4-4451-B9D8-77123F274797}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{993C3930-A6E5-42FC-BE9E-A7FB6D6559E8}"/>
+    <hyperlink ref="B14" r:id="rId2" xr:uid="{BD532200-316F-4AF8-9654-CB7E59CB5D20}"/>
+    <hyperlink ref="B21" r:id="rId3" xr:uid="{22BDA847-0FC8-4E69-AF35-10521D5C92C7}"/>
+    <hyperlink ref="B28" r:id="rId4" xr:uid="{707A1C22-C44E-4726-BE47-D76D8D7B82D7}"/>
+    <hyperlink ref="B35" r:id="rId5" xr:uid="{1E91072C-C999-40CE-AD3D-03EAF7A7F19C}"/>
+    <hyperlink ref="B42" r:id="rId6" xr:uid="{8A822303-5EBA-4628-910E-4AD80C06B16B}"/>
+    <hyperlink ref="B49" r:id="rId7" xr:uid="{13C829DD-B5BF-4F57-B0FE-69C715CEC333}"/>
+    <hyperlink ref="D7" r:id="rId8" xr:uid="{577A53AF-16ED-4D54-AE25-7DF41F495315}"/>
+    <hyperlink ref="D14" r:id="rId9" xr:uid="{F9792ED1-759A-4B26-99B5-7EA07B2912A7}"/>
+    <hyperlink ref="D21" r:id="rId10" xr:uid="{68BAC0F7-5F73-4119-B5C2-559B44FD183B}"/>
+    <hyperlink ref="D28" r:id="rId11" xr:uid="{88E06003-5D84-442B-B94B-7284B3367D01}"/>
+    <hyperlink ref="D35" r:id="rId12" xr:uid="{7DA977F1-8DBC-437A-A467-F542E6934F8A}"/>
+    <hyperlink ref="D42" r:id="rId13" xr:uid="{58181472-D502-40A9-AEEE-B33365AAC262}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1317,19 +1322,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="87.5703125" customWidth="1"/>
+    <col min="8" max="8" width="87.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>73</v>
       </c>
@@ -1337,12 +1342,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="116" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>75</v>
       </c>
@@ -1368,7 +1373,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -1391,7 +1396,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>85</v>
       </c>
@@ -1408,10 +1413,10 @@
         <v>1700</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>87</v>
       </c>
@@ -1425,8 +1430,8 @@
         <v>86</v>
       </c>
       <c r="E7">
-        <f>ROUND((2100/391)^(1/(2070-2023))-1,3)</f>
-        <v>3.5999999999999997E-2</v>
+        <f>((2100/391)^(1/(2070-2023))-1)</f>
+        <v>3.6412923934614927E-2</v>
       </c>
       <c r="F7" t="s">
         <v>88</v>
@@ -1435,10 +1440,10 @@
         <v>470</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>89</v>
       </c>
@@ -1452,10 +1457,10 @@
         <v>82</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>90</v>
       </c>
@@ -1475,7 +1480,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>92</v>
       </c>
@@ -1498,10 +1503,10 @@
         <v>67</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>93</v>
       </c>
@@ -1518,10 +1523,10 @@
         <v>42</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>94</v>
       </c>
@@ -1545,7 +1550,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -1562,10 +1567,10 @@
         <v>64</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>97</v>
       </c>
@@ -1586,17 +1591,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -1616,7 +1621,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -1636,7 +1641,7 @@
         <v>84000</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>103</v>
       </c>
@@ -1656,7 +1661,7 @@
         <v>69000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>104</v>
       </c>
@@ -1676,7 +1681,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>105</v>
       </c>
@@ -1696,7 +1701,7 @@
         <v>23000</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -1716,7 +1721,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>107</v>
       </c>
@@ -1736,7 +1741,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>108</v>
       </c>
@@ -1756,7 +1761,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>109</v>
       </c>
@@ -1776,7 +1781,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>110</v>
       </c>
@@ -1796,7 +1801,7 @@
         <v>8200</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>111</v>
       </c>
@@ -1816,7 +1821,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>112</v>
       </c>
@@ -1833,7 +1838,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>117</v>
       </c>
@@ -1850,7 +1855,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -1867,7 +1872,7 @@
         <v>61000</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>85</v>
       </c>
@@ -1884,7 +1889,7 @@
         <v>1800000</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>118</v>
       </c>
@@ -1901,7 +1906,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>87</v>
       </c>
@@ -1918,7 +1923,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>96</v>
       </c>
@@ -1935,7 +1940,7 @@
         <v>83000</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>119</v>
       </c>
@@ -1952,7 +1957,7 @@
         <v>85000</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>90</v>
       </c>
@@ -1969,7 +1974,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>120</v>
       </c>
@@ -1986,7 +1991,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>93</v>
       </c>
@@ -2003,7 +2008,7 @@
         <v>42000</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>121</v>
       </c>
@@ -2020,7 +2025,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>122</v>
       </c>
@@ -2037,7 +2042,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>123</v>
       </c>
@@ -2054,7 +2059,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>124</v>
       </c>
@@ -2071,7 +2076,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>125</v>
       </c>
@@ -2088,7 +2093,7 @@
         <v>650000</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>126</v>
       </c>
@@ -2113,14 +2118,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AD4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>128</v>
       </c>
@@ -2212,7 +2217,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>132</v>
       </c>
@@ -2312,12 +2317,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AE11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>136</v>
       </c>
@@ -2326,7 +2331,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>76</v>
       </c>
@@ -2335,7 +2340,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>137</v>
       </c>
@@ -2344,7 +2349,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>138</v>
       </c>
@@ -2353,7 +2358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>139</v>
       </c>
@@ -2362,7 +2367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>140</v>
       </c>
@@ -2457,7 +2462,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>141</v>
       </c>
@@ -2482,7 +2487,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>142</v>
       </c>
@@ -2591,7 +2596,7 @@
         <v>1.149171912206338</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>143</v>
       </c>
@@ -2716,7 +2721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>144</v>
       </c>
@@ -2852,11 +2857,11 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -2949,129 +2954,129 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>145</v>
       </c>
       <c r="B2">
-        <f>ROUND(Derivation!B11,0)</f>
+        <f>(Derivation!B11)</f>
         <v>111000000</v>
       </c>
       <c r="C2">
-        <f>ROUND(Derivation!C11,0)</f>
+        <f>(Derivation!C11)</f>
         <v>114000000</v>
       </c>
       <c r="D2">
-        <f>ROUND(Derivation!D11,0)</f>
+        <f>(Derivation!D11)</f>
         <v>113000000</v>
       </c>
       <c r="E2">
-        <f>ROUND(Derivation!E11,0)</f>
+        <f>(Derivation!E11)</f>
         <v>110000000</v>
       </c>
       <c r="F2">
-        <f>ROUND(Derivation!F11,0)</f>
+        <f>(Derivation!F11)</f>
         <v>110000000</v>
       </c>
       <c r="G2">
-        <f>ROUND(Derivation!G11,0)</f>
-        <v>107675609</v>
+        <f>(Derivation!G11)</f>
+        <v>107675608.69307683</v>
       </c>
       <c r="H2">
-        <f>ROUND(Derivation!H11,0)</f>
-        <v>105767322</v>
+        <f>(Derivation!H11)</f>
+        <v>105767321.58122508</v>
       </c>
       <c r="I2">
-        <f>ROUND(Derivation!I11,0)</f>
-        <v>104859577</v>
+        <f>(Derivation!I11)</f>
+        <v>104859576.77714515</v>
       </c>
       <c r="J2">
-        <f>ROUND(Derivation!J11,0)</f>
-        <v>104372166</v>
+        <f>(Derivation!J11)</f>
+        <v>104372166.01880008</v>
       </c>
       <c r="K2">
-        <f>ROUND(Derivation!K11,0)</f>
-        <v>104616472</v>
+        <f>(Derivation!K11)</f>
+        <v>104616472.29597773</v>
       </c>
       <c r="L2">
-        <f>ROUND(Derivation!L11,0)</f>
-        <v>105333544</v>
+        <f>(Derivation!L11)</f>
+        <v>105333543.91541499</v>
       </c>
       <c r="M2">
-        <f>ROUND(Derivation!M11,0)</f>
-        <v>106324425</v>
+        <f>(Derivation!M11)</f>
+        <v>106324424.72584967</v>
       </c>
       <c r="N2">
-        <f>ROUND(Derivation!N11,0)</f>
-        <v>107634842</v>
+        <f>(Derivation!N11)</f>
+        <v>107634841.88723963</v>
       </c>
       <c r="O2">
-        <f>ROUND(Derivation!O11,0)</f>
-        <v>109087177</v>
+        <f>(Derivation!O11)</f>
+        <v>109087177.01866114</v>
       </c>
       <c r="P2">
-        <f>ROUND(Derivation!P11,0)</f>
-        <v>110633028</v>
+        <f>(Derivation!P11)</f>
+        <v>110633028.37491795</v>
       </c>
       <c r="Q2">
-        <f>ROUND(Derivation!Q11,0)</f>
-        <v>112222463</v>
+        <f>(Derivation!Q11)</f>
+        <v>112222462.51001629</v>
       </c>
       <c r="R2">
-        <f>ROUND(Derivation!R11,0)</f>
-        <v>113787154</v>
+        <f>(Derivation!R11)</f>
+        <v>113787153.78608054</v>
       </c>
       <c r="S2">
-        <f>ROUND(Derivation!S11,0)</f>
-        <v>115386956</v>
+        <f>(Derivation!S11)</f>
+        <v>115386956.35734558</v>
       </c>
       <c r="T2">
-        <f>ROUND(Derivation!T11,0)</f>
-        <v>116947194</v>
+        <f>(Derivation!T11)</f>
+        <v>116947193.91878366</v>
       </c>
       <c r="U2">
-        <f>ROUND(Derivation!U11,0)</f>
-        <v>118253688</v>
+        <f>(Derivation!U11)</f>
+        <v>118253687.56966965</v>
       </c>
       <c r="V2">
-        <f>ROUND(Derivation!V11,0)</f>
-        <v>119253924</v>
+        <f>(Derivation!V11)</f>
+        <v>119253923.53728199</v>
       </c>
       <c r="W2">
-        <f>ROUND(Derivation!W11,0)</f>
-        <v>119928485</v>
+        <f>(Derivation!W11)</f>
+        <v>119928484.56843579</v>
       </c>
       <c r="X2">
-        <f>ROUND(Derivation!X11,0)</f>
-        <v>120167124</v>
+        <f>(Derivation!X11)</f>
+        <v>120167123.55266325</v>
       </c>
       <c r="Y2">
-        <f>ROUND(Derivation!Y11,0)</f>
-        <v>120126663</v>
+        <f>(Derivation!Y11)</f>
+        <v>120126663.0869855</v>
       </c>
       <c r="Z2">
-        <f>ROUND(Derivation!Z11,0)</f>
-        <v>120446211</v>
+        <f>(Derivation!Z11)</f>
+        <v>120446211.22025461</v>
       </c>
       <c r="AA2">
-        <f>ROUND(Derivation!AA11,0)</f>
-        <v>121228533</v>
+        <f>(Derivation!AA11)</f>
+        <v>121228533.29365906</v>
       </c>
       <c r="AB2">
-        <f>ROUND(Derivation!AB11,0)</f>
-        <v>122314780</v>
+        <f>(Derivation!AB11)</f>
+        <v>122314780.15219964</v>
       </c>
       <c r="AC2">
-        <f>ROUND(Derivation!AC11,0)</f>
-        <v>123593338</v>
+        <f>(Derivation!AC11)</f>
+        <v>123593337.9370047</v>
       </c>
       <c r="AD2">
-        <f>ROUND(Derivation!AD11,0)</f>
-        <v>124961983</v>
+        <f>(Derivation!AD11)</f>
+        <v>124961983.29332167</v>
       </c>
       <c r="AE2">
-        <f>ROUND(Derivation!AE11,0)</f>
-        <v>126408910</v>
+        <f>(Derivation!AE11)</f>
+        <v>126408910.34269717</v>
       </c>
     </row>
   </sheetData>
